--- a/sources/ganryu_step10.xlsx
+++ b/sources/ganryu_step10.xlsx
@@ -883,6 +883,11 @@
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
@@ -955,6 +960,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
@@ -1027,6 +1037,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
@@ -1089,6 +1104,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
@@ -1154,6 +1174,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
